--- a/bakup/customers/bofon.xlsx
+++ b/bakup/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="199">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -583,6 +583,39 @@
   </si>
   <si>
     <t>بستنی لیموناد</t>
+  </si>
+  <si>
+    <t>1405/06/06</t>
+  </si>
+  <si>
+    <t>الباقی سیگار پفک</t>
+  </si>
+  <si>
+    <t>1405/06/07</t>
+  </si>
+  <si>
+    <t>دنگ سوسیس خونه یاسین</t>
+  </si>
+  <si>
+    <t>1405/06/24</t>
+  </si>
+  <si>
+    <t>1405/06/25</t>
+  </si>
+  <si>
+    <t>سیگار</t>
+  </si>
+  <si>
+    <t>1405/06/27</t>
+  </si>
+  <si>
+    <t>وجه عرق</t>
+  </si>
+  <si>
+    <t>1405/07/02</t>
+  </si>
+  <si>
+    <t>بستنی کیک</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1162,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3165,77 +3198,115 @@
     <row r="146" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="8">
         <f xml:space="preserve"> A145+B146-C146</f>
-        <v>2924600</v>
-      </c>
-      <c r="B146" s="8"/>
+        <v>3074600</v>
+      </c>
+      <c r="B146" s="8">
+        <v>150000</v>
+      </c>
       <c r="C146" s="8"/>
-      <c r="D146" s="1"/>
-      <c r="E146" s="1"/>
+      <c r="D146" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="147" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="8">
         <f t="shared" ref="A147:A164" si="6" xml:space="preserve"> A146+B147-C147</f>
-        <v>2924600</v>
-      </c>
-      <c r="B147" s="8"/>
+        <v>3190600</v>
+      </c>
+      <c r="B147" s="8">
+        <v>116000</v>
+      </c>
       <c r="C147" s="8"/>
-      <c r="D147" s="1"/>
-      <c r="E147" s="1"/>
+      <c r="D147" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="148" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
-      </c>
-      <c r="B148" s="8"/>
+        <v>3302600</v>
+      </c>
+      <c r="B148" s="8">
+        <v>112000</v>
+      </c>
       <c r="C148" s="8"/>
       <c r="D148" s="1"/>
-      <c r="E148" s="1"/>
+      <c r="E148" s="1" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="149" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
-      </c>
-      <c r="B149" s="8"/>
+        <v>3452600</v>
+      </c>
+      <c r="B149" s="8">
+        <v>150000</v>
+      </c>
       <c r="C149" s="8"/>
-      <c r="D149" s="1"/>
-      <c r="E149" s="1"/>
+      <c r="D149" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>2952600</v>
       </c>
       <c r="B150" s="8"/>
-      <c r="C150" s="8"/>
-      <c r="D150" s="1"/>
-      <c r="E150" s="1"/>
+      <c r="C150" s="8">
+        <v>500000</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
-      </c>
-      <c r="B151" s="8"/>
+        <v>3102600</v>
+      </c>
+      <c r="B151" s="8">
+        <v>150000</v>
+      </c>
       <c r="C151" s="8"/>
-      <c r="D151" s="1"/>
+      <c r="D151" s="1" t="s">
+        <v>194</v>
+      </c>
       <c r="E151" s="1"/>
     </row>
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
-      </c>
-      <c r="B152" s="8"/>
+        <v>3282600</v>
+      </c>
+      <c r="B152" s="8">
+        <v>180000</v>
+      </c>
       <c r="C152" s="8"/>
-      <c r="D152" s="1"/>
-      <c r="E152" s="1"/>
+      <c r="D152" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -3245,7 +3316,7 @@
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -3255,7 +3326,7 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3265,7 +3336,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3275,7 +3346,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3285,7 +3356,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3295,7 +3366,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3305,7 +3376,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3315,7 +3386,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3325,7 +3396,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3335,7 +3406,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3345,7 +3416,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3356,18 +3427,18 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>14825600</v>
+        <v>15683600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
-        <v>11901000</v>
+        <v>12401000</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>
